--- a/4_pagos/efectivo/inputs/entregas_hoja.xlsx
+++ b/4_pagos/efectivo/inputs/entregas_hoja.xlsx
@@ -1,135 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilde\PycharmProjects\jass_system\4_pagos\efectivo\inputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE468B3-9FC1-4046-A09D-B309A06B21D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28230" yWindow="570" windowWidth="14610" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28230" yWindow="570" windowWidth="14610" windowHeight="15480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Entregas" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entregas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
-  <si>
-    <t>¿Quién y cuándo?</t>
-  </si>
-  <si>
-    <t>¿Cuánto recibió?</t>
-  </si>
-  <si>
-    <t>¿Corrección?</t>
-  </si>
-  <si>
-    <t>Sistema — no tocar</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>COBRADOR</t>
-  </si>
-  <si>
-    <t>EFECTIVO</t>
-  </si>
-  <si>
-    <t>YAPE</t>
-  </si>
-  <si>
-    <t>MOTIVO</t>
-  </si>
-  <si>
-    <t>IMPORTADO</t>
-  </si>
-  <si>
-    <t>04/07/2026</t>
-  </si>
-  <si>
-    <t>Maximo Encarnacion</t>
-  </si>
-  <si>
-    <t>Wilder Trujillo</t>
-  </si>
-  <si>
-    <t>Yerald Romero</t>
-  </si>
-  <si>
-    <t>Wagner Trujillo</t>
-  </si>
-  <si>
-    <t>confirmado</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1A5276"/>
       <sz val="9"/>
-      <color rgb="FF1A5276"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1E5C3A"/>
       <sz val="9"/>
-      <color rgb="FF1E5C3A"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF880E4F"/>
       <sz val="9"/>
-      <color rgb="FF880E4F"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF374151"/>
       <sz val="9"/>
-      <color rgb="FF374151"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF9CA3AF"/>
       <sz val="10"/>
-      <color rgb="FF9CA3AF"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -168,52 +96,131 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>verificar_lotes</author>
+  </authors>
+  <commentList>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Asumido = lo que mesa_2.xlsx registra que Yerald cobro ese dia. No hay declaracion de la tesorera ("Recibi X") legible en las fotos de la hoja de papel, a diferencia de Wilder. Si aparece un sobrante o faltante real, corregir con MOTIVO (columna de correccion).</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Asumido = lo que mesa_2.xlsx registra que Yerald cobro ese dia. No hay declaracion de la tesorera ("Recibi X") legible en las fotos de la hoja de papel, a diferencia de Wilder. Si aparece un sobrante o faltante real, corregir con MOTIVO (columna de correccion).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -500,253 +507,185 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
+    <col width="14" customWidth="1" style="11" min="1" max="1"/>
+    <col width="22" customWidth="1" style="11" min="2" max="2"/>
+    <col width="12" customWidth="1" style="11" min="3" max="4"/>
+    <col width="30" customWidth="1" style="11" min="5" max="5"/>
+    <col width="34" customWidth="1" style="11" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" ht="18" customHeight="1" s="11">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>¿Quién y cuándo?</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>¿Cuánto recibió?</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>¿Corrección?</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Sistema — no tocar</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1" s="11">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>COBRADOR</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>EFECTIVO</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>YAPE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>MOTIVO</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>IMPORTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Maximo Encarnacion</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>2935</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Wilder Trujillo</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>621</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wilder Trujillo</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>595</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yerald Romero</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>818</v>
+      </c>
+      <c r="D6" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="7">
-        <v>2935</v>
-      </c>
-      <c r="D3" s="7">
-        <v>200</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>379</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>390</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>695</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>503</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>644</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>473</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10">
-        <v>483</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
-        <v>832</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12">
-        <v>678</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13">
-        <v>969</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="9">
-        <v>46208</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15">
-        <v>817</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="9">
-        <v>46208</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16">
-        <v>448</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="9">
-        <v>46208</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17">
-        <v>373</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yerald Romero</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1643</v>
+      </c>
+      <c r="D7" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -754,5 +693,6 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/4_pagos/efectivo/inputs/entregas_hoja.xlsx
+++ b/4_pagos/efectivo/inputs/entregas_hoja.xlsx
@@ -217,6 +217,21 @@
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
         <t>Asumido = lo que mesa_2.xlsx registra que Yerald cobro ese dia. No hay declaracion de la tesorera ("Recibi X") legible en las fotos de la hoja de papel, a diferencia de Wilder. Si aparece un sobrante o faltante real, corregir con MOTIVO (columna de correccion).</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Asumido = lo que mesa_3.xlsx registra que Maximo cobro ese dia. No hay declaracion de la secretaria ("Recibi X") legible en las fotos de la hoja de papel, a diferencia de Wilder. Si aparece un sobrante o faltante real, corregir con MOTIVO (columna de correccion).</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Asumido = lo que mesa_3.xlsx registra que Maximo cobro ese dia. No hay declaracion de la secretaria ("Recibi X") legible en las fotos de la hoja de papel, a diferencia de Wilder. Si aparece un sobrante o faltante real, corregir con MOTIVO (columna de correccion).</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>Asumido = lo que mesa_4.xlsx registra que Wagner cobro ese dia. No hay declaracion de la secretaria ("Recibi X") legible en las fotos de la hoja de papel para esta fecha. Si aparece un sobrante o faltante real, corregir con MOTIVO (columna de correccion).</t>
       </text>
     </comment>
   </commentList>
@@ -661,16 +676,68 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n"/>
+      <c r="A8" s="9" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Maximo Encarnacion</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1516</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
+      <c r="A9" s="9" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Maximo Encarnacion</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>579</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
+      <c r="A10" s="9" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wagner Trujillo</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>341</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
+      <c r="A11" s="9" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wagner Trujillo</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>626</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n"/>
@@ -678,6 +745,7 @@
     <row r="13">
       <c r="A13" s="9" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="9" t="n"/>
     </row>
